--- a/docs/d/U/inyear.xlsx
+++ b/docs/d/U/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/U/inyear.xlsx
+++ b/docs/d/U/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1737,11 @@
       <c r="AB10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AC10" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2248,7 +2252,11 @@
       <c r="AB15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC15" s="4" t="inlineStr"/>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">

--- a/docs/d/U/inyear.xlsx
+++ b/docs/d/U/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 20 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 19 clubs short</t>
         </is>
       </c>
     </row>
@@ -1876,17 +1876,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M12" s="7" t="n">
@@ -1924,7 +1924,7 @@
         <v>4</v>
       </c>
       <c r="W12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" s="9" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="X15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3239,8 +3239,8 @@
       <c r="S25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T25" s="9" t="n">
-        <v>0</v>
+      <c r="T25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U25" s="9" t="n">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3560,8 +3560,8 @@
       <c r="Y28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z28" s="9" t="n">
-        <v>0</v>
+      <c r="Z28" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA28" s="10" t="n">
         <v>1</v>
@@ -3808,7 +3808,7 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -3925,7 +3925,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>

--- a/docs/d/U/inyear.xlsx
+++ b/docs/d/U/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 19 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 15 clubs short</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>10</v>
@@ -1324,8 +1324,8 @@
       <c r="Y6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z6" s="9" t="n">
-        <v>0</v>
+      <c r="Z6" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA6" s="10" t="n">
         <v>1</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1905,20 +1905,20 @@
       <c r="P12" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q12" s="9" t="n">
-        <v>1</v>
+      <c r="Q12" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R12" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U12" s="9" t="n">
-        <v>0</v>
+      <c r="U12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V12" s="10" t="n">
         <v>4</v>
@@ -1926,14 +1926,14 @@
       <c r="W12" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="X12" s="9" t="n">
-        <v>0</v>
+      <c r="X12" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" s="9" t="n">
-        <v>0</v>
+      <c r="Z12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA12" s="10" t="n">
         <v>1</v>
@@ -2142,8 +2142,8 @@
       <c r="Y14" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z14" s="9" t="n">
-        <v>0</v>
+      <c r="Z14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA14" s="9" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2225,8 +2225,8 @@
       <c r="S15" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="T15" s="9" t="n">
-        <v>0</v>
+      <c r="T15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U15" s="9" t="n">
         <v>0</v>
@@ -2237,8 +2237,8 @@
       <c r="W15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X15" s="9" t="n">
-        <v>1</v>
+      <c r="X15" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y15" s="9" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Virtual Professional Speakers</t>
+          <t>Virtual Professional Speakers - Online Toastmasters Club</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
@@ -3358,8 +3358,8 @@
       <c r="Y26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z26" s="9" t="n">
-        <v>0</v>
+      <c r="Z26" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA26" s="9" t="n">
         <v>0</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3531,16 +3531,16 @@
         </is>
       </c>
       <c r="P28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q28" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S28" s="9" t="n">
-        <v>0</v>
+      <c r="S28" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T28" s="9" t="n">
         <v>0</v>
@@ -3793,13 +3793,13 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -3958,7 +3958,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>

--- a/docs/d/U/inyear.xlsx
+++ b/docs/d/U/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 15 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 15 clubs short</t>
         </is>
       </c>
     </row>
@@ -1062,17 +1062,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="7" t="n">
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="V4" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1167,13 +1167,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
@@ -1268,13 +1268,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>0</v>
       </c>
       <c r="V6" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W6" s="9" t="n">
         <v>0</v>
@@ -1557,7 +1557,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1571,13 +1571,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L9" s="8" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>1</v>
       </c>
       <c r="Q9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="9" t="n">
         <v>0</v>
@@ -1609,8 +1609,8 @@
       <c r="S9" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T9" s="9" t="n">
-        <v>0</v>
+      <c r="T9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U9" s="9" t="n">
         <v>0</v>
@@ -1672,13 +1672,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1777,17 +1777,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M11" s="7" t="n">
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1876,17 +1876,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="7" t="n">
@@ -1911,8 +1911,8 @@
       <c r="R12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S12" s="9" t="n">
-        <v>1</v>
+      <c r="S12" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T12" s="10" t="n">
         <v>1</v>
@@ -1981,13 +1981,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
+        <v>-10</v>
       </c>
       <c r="L13" s="8" t="inlineStr">
         <is>
@@ -2086,13 +2086,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L14" s="8" t="inlineStr">
         <is>
@@ -2187,13 +2187,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2292,13 +2292,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="S16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" s="9" t="n">
         <v>0</v>
@@ -2393,13 +2393,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
@@ -2696,13 +2696,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2797,17 +2797,17 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L21" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-13</v>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M21" s="7" t="n">
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -3100,13 +3100,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
@@ -3201,13 +3201,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>10</v>
@@ -3302,17 +3302,17 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>11</v>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M26" s="7" t="n">
@@ -3346,11 +3346,11 @@
       <c r="U26" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V26" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="9" t="n">
-        <v>0</v>
+      <c r="V26" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W26" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X26" s="9" t="n">
         <v>0</v>
@@ -3403,13 +3403,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3504,13 +3504,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3548,11 +3548,11 @@
       <c r="U28" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V28" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" s="9" t="n">
-        <v>0</v>
+      <c r="V28" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W28" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="X28" s="9" t="n">
         <v>0</v>
@@ -3591,7 +3591,7 @@
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F29" s="6" t="n">
         <v>10</v>
@@ -3605,13 +3605,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -3649,11 +3649,11 @@
       <c r="U29" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" s="9" t="n">
-        <v>0</v>
+      <c r="V29" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W29" s="10" t="n">
+        <v>13</v>
       </c>
       <c r="X29" s="9" t="n">
         <v>0</v>
@@ -3793,7 +3793,7 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3808,7 +3808,7 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -3907,7 +3907,7 @@
         <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3958,13 +3958,13 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>0.75</v>
+        <v>2.25</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -3973,7 +3973,7 @@
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/U/inyear.xlsx
+++ b/docs/d/U/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/U/inyear.xlsx
+++ b/docs/d/U/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/U/inyear.xlsx
+++ b/docs/d/U/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:57 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/U/inyear.xlsx
+++ b/docs/d/U/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/U/inyear.xlsx
+++ b/docs/d/U/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 15 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 15 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -1062,13 +1062,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L4" s="8" t="inlineStr">
         <is>
@@ -1672,13 +1672,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -2173,7 +2173,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2228,8 +2228,8 @@
       <c r="T15" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U15" s="9" t="n">
-        <v>0</v>
+      <c r="U15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V15" s="9" t="n">
         <v>2</v>
@@ -3490,7 +3490,7 @@
         </is>
       </c>
       <c r="E28" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>10</v>
@@ -3504,13 +3504,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -3530,8 +3530,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P28" s="9" t="n">
-        <v>2</v>
+      <c r="P28" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Q28" s="10" t="n">
         <v>2</v>
@@ -3552,7 +3552,7 @@
         <v>4</v>
       </c>
       <c r="W28" s="10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X28" s="9" t="n">
         <v>0</v>
@@ -3793,7 +3793,7 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3958,7 +3958,7 @@
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>

--- a/docs/d/U/inyear.xlsx
+++ b/docs/d/U/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 11 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 11 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 15 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 15 clubs short</t>
         </is>
       </c>
     </row>
@@ -1672,13 +1672,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="P10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" s="9" t="n">
         <v>0</v>
@@ -1720,7 +1720,7 @@
         <v>4</v>
       </c>
       <c r="W10" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" s="9" t="n">
         <v>3</v>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1777,17 +1777,17 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L11" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>6</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M11" s="7" t="n">
@@ -1824,8 +1824,8 @@
       <c r="V11" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W11" s="9" t="n">
-        <v>1</v>
+      <c r="W11" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X11" s="9" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>2</v>
       </c>
       <c r="R12" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" s="10" t="n">
         <v>2</v>
@@ -2214,7 +2214,7 @@
         </is>
       </c>
       <c r="P15" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="9" t="n">
         <v>0</v>
@@ -2292,13 +2292,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-12</v>
+        <v>-9</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         </is>
       </c>
       <c r="P16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16" s="9" t="n">
         <v>0</v>
@@ -2337,7 +2337,7 @@
         <v>0</v>
       </c>
       <c r="V16" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="9" t="n">
         <v>0</v>
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L23" s="8" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -3808,7 +3808,7 @@
         <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
